--- a/LCA Exports/GasFerment_InventoryAssessment.xlsx
+++ b/LCA Exports/GasFerment_InventoryAssessment.xlsx
@@ -900,7 +900,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Low Pressure Steam (seed only)</t>
+          <t>Natural Gas, boiler (seed only)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -915,14 +915,14 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>kg_ng</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>411.89754057</v>
+        <v>27.2348116</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1289342908</v>
+        <v>0.008525181099999999</v>
       </c>
     </row>
     <row r="12">
